--- a/artfynd/A 13005-2025 artfynd.xlsx
+++ b/artfynd/A 13005-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68986098</v>
+        <v>68986090</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382200.1916506577</v>
+        <v>382212</v>
       </c>
       <c r="R2" t="n">
-        <v>6350292.813530394</v>
+        <v>6350303</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marcus Arnesson, Sandra Nilsson</t>
+          <t>Sandra Nilsson, Marcus Arnesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +780,7 @@
         <v>68986099</v>
       </c>
       <c r="B3" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382231.1947495849</v>
+        <v>382231</v>
       </c>
       <c r="R3" t="n">
-        <v>6350296.791347792</v>
+        <v>6350297</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +845,9 @@
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -902,22 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marcus Arnesson, Sandra Nilsson</t>
+          <t>Sandra Nilsson, Marcus Arnesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68986090</v>
+        <v>68986098</v>
       </c>
       <c r="B4" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>382211.8571182411</v>
+        <v>382200</v>
       </c>
       <c r="R4" t="n">
-        <v>6350302.754771539</v>
+        <v>6350293</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1019,22 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marcus Arnesson, Sandra Nilsson</t>
+          <t>Sandra Nilsson, Marcus Arnesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68986097</v>
+        <v>68986100</v>
       </c>
       <c r="B5" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,16 +992,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>382209.2118400281</v>
+        <v>382200</v>
       </c>
       <c r="R5" t="n">
-        <v>6350304.994075444</v>
+        <v>6350307</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,19 +1049,9 @@
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1136,10 +1076,112 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marcus Arnesson, Sandra Nilsson</t>
+          <t>Sandra Nilsson, Marcus Arnesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>68986097</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Arvidstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>382209</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6350305</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Svenljunga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kalv</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Inventering utförd av Ecocom AB på uppdrag av Svenljunga kommun.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sandra Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sandra Nilsson, Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13005-2025 artfynd.xlsx
+++ b/artfynd/A 13005-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68986090</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68986099</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68986098</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68986100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68986097</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>